--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121776204</v>
+        <v>121780985</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544311</v>
+        <v>544320</v>
       </c>
       <c r="R2" t="n">
-        <v>6599894</v>
+        <v>6599846</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,39 +752,30 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -917,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121780985</v>
+        <v>121781128</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,31 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544320</v>
+        <v>544423</v>
       </c>
       <c r="R4" t="n">
-        <v>6599846</v>
+        <v>6599802</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +995,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121780398</v>
+        <v>121780824</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>8436</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,21 +1029,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544439</v>
+        <v>544335</v>
       </c>
       <c r="R5" t="n">
-        <v>6599807</v>
+        <v>6599931</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,7 +1125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121781128</v>
+        <v>121780897</v>
       </c>
       <c r="B6" t="n">
         <v>57373</v>
@@ -1184,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544423</v>
+        <v>544338</v>
       </c>
       <c r="R6" t="n">
-        <v>6599802</v>
+        <v>6599919</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121780897</v>
+        <v>121780398</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,33 +1247,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1294,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544338</v>
+        <v>544439</v>
       </c>
       <c r="R7" t="n">
-        <v>6599919</v>
+        <v>6599807</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,6 +1328,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1356,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121774673</v>
+        <v>121776204</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1391,7 +1382,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1399,19 +1390,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544346</v>
+        <v>544311</v>
       </c>
       <c r="R8" t="n">
-        <v>6599874</v>
+        <v>6599894</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1453,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,7 +1450,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1481,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121780824</v>
+        <v>121774673</v>
       </c>
       <c r="B9" t="n">
-        <v>8436</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,47 +1480,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544335</v>
+        <v>544346</v>
       </c>
       <c r="R9" t="n">
-        <v>6599931</v>
+        <v>6599874</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,9 +1553,19 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,12 +1581,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121780985</v>
+        <v>121780824</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>8436</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544320</v>
+        <v>544335</v>
       </c>
       <c r="R2" t="n">
-        <v>6599846</v>
+        <v>6599931</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121776215</v>
+        <v>121781128</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,47 +799,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544309</v>
+        <v>544423</v>
       </c>
       <c r="R3" t="n">
-        <v>6599888</v>
+        <v>6599802</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +868,9 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121781128</v>
+        <v>121780985</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +909,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544423</v>
+        <v>544320</v>
       </c>
       <c r="R4" t="n">
-        <v>6599802</v>
+        <v>6599846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,6 +985,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1013,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121780824</v>
+        <v>121780897</v>
       </c>
       <c r="B5" t="n">
-        <v>8436</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,34 +1016,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1062,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544335</v>
+        <v>544338</v>
       </c>
       <c r="R5" t="n">
-        <v>6599931</v>
+        <v>6599919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1096,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121780897</v>
+        <v>121776215</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,46 +1126,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544338</v>
+        <v>544309</v>
       </c>
       <c r="R6" t="n">
-        <v>6599919</v>
+        <v>6599888</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,9 +1196,19 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,22 +1223,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121780398</v>
+        <v>121774673</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,47 +1247,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544439</v>
+        <v>544346</v>
       </c>
       <c r="R7" t="n">
-        <v>6599807</v>
+        <v>6599874</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,9 +1320,19 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,12 +1348,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1468,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121774673</v>
+        <v>121780398</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,50 +1493,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544346</v>
+        <v>544439</v>
       </c>
       <c r="R9" t="n">
-        <v>6599874</v>
+        <v>6599807</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,19 +1563,9 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,12 +1581,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121780824</v>
+        <v>121781128</v>
       </c>
       <c r="B2" t="n">
-        <v>8436</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -724,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544335</v>
+        <v>544423</v>
       </c>
       <c r="R2" t="n">
-        <v>6599931</v>
+        <v>6599802</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121781128</v>
+        <v>121780897</v>
       </c>
       <c r="B3" t="n">
         <v>57373</v>
@@ -835,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544423</v>
+        <v>544338</v>
       </c>
       <c r="R3" t="n">
-        <v>6599802</v>
+        <v>6599919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121780985</v>
+        <v>121774673</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,42 +907,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544320</v>
+        <v>544346</v>
       </c>
       <c r="R4" t="n">
-        <v>6599846</v>
+        <v>6599874</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,9 +980,19 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121780897</v>
+        <v>121780824</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>8436</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,33 +1032,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1052,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544338</v>
+        <v>544335</v>
       </c>
       <c r="R5" t="n">
-        <v>6599919</v>
+        <v>6599931</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,6 +1113,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1235,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121774673</v>
+        <v>121780398</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,50 +1265,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544346</v>
+        <v>544439</v>
       </c>
       <c r="R7" t="n">
-        <v>6599874</v>
+        <v>6599807</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,19 +1335,9 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,22 +1353,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121776204</v>
+        <v>121780985</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>97067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,47 +1377,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544311</v>
+        <v>544320</v>
       </c>
       <c r="R8" t="n">
-        <v>6599894</v>
+        <v>6599846</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,49 +1442,40 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121780398</v>
+        <v>121776204</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,47 +1484,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544439</v>
+        <v>544311</v>
       </c>
       <c r="R9" t="n">
-        <v>6599807</v>
+        <v>6599894</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,30 +1554,39 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121781128</v>
+        <v>121776215</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544423</v>
+        <v>544309</v>
       </c>
       <c r="R2" t="n">
-        <v>6599802</v>
+        <v>6599888</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,9 +757,19 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121780897</v>
+        <v>121776204</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,46 +808,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544338</v>
+        <v>544311</v>
       </c>
       <c r="R3" t="n">
-        <v>6599919</v>
+        <v>6599894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,9 +878,19 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,22 +905,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121774673</v>
+        <v>121780398</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,50 +929,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544346</v>
+        <v>544439</v>
       </c>
       <c r="R4" t="n">
-        <v>6599874</v>
+        <v>6599807</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +999,9 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +1017,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121780824</v>
+        <v>121781128</v>
       </c>
       <c r="B5" t="n">
-        <v>8436</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1041,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1069,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544335</v>
+        <v>544423</v>
       </c>
       <c r="R5" t="n">
-        <v>6599931</v>
+        <v>6599802</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1121,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1132,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121776215</v>
+        <v>121780897</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,47 +1151,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544309</v>
+        <v>544338</v>
       </c>
       <c r="R6" t="n">
-        <v>6599888</v>
+        <v>6599919</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,19 +1220,9 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,22 +1237,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121780398</v>
+        <v>121780824</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>8436</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,21 +1265,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544439</v>
+        <v>544335</v>
       </c>
       <c r="R7" t="n">
-        <v>6599807</v>
+        <v>6599931</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1472,7 +1468,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121776204</v>
+        <v>121774673</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1507,7 +1503,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1515,16 +1511,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544311</v>
+        <v>544346</v>
       </c>
       <c r="R9" t="n">
-        <v>6599894</v>
+        <v>6599874</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,6 +1574,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121776215</v>
+        <v>121781128</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544309</v>
+        <v>544423</v>
       </c>
       <c r="R2" t="n">
-        <v>6599888</v>
+        <v>6599802</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +756,9 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +773,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121776204</v>
+        <v>121780897</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,47 +797,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544311</v>
+        <v>544338</v>
       </c>
       <c r="R3" t="n">
-        <v>6599894</v>
+        <v>6599919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,19 +866,9 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,22 +883,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121780398</v>
+        <v>121780824</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>8436</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -966,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544439</v>
+        <v>544335</v>
       </c>
       <c r="R4" t="n">
-        <v>6599807</v>
+        <v>6599931</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121781128</v>
+        <v>121776204</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,46 +1019,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544423</v>
+        <v>544311</v>
       </c>
       <c r="R5" t="n">
-        <v>6599802</v>
+        <v>6599894</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,9 +1089,19 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121780897</v>
+        <v>121774673</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,46 +1140,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544338</v>
+        <v>544346</v>
       </c>
       <c r="R6" t="n">
-        <v>6599919</v>
+        <v>6599874</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,39 +1213,50 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121780824</v>
+        <v>121776215</v>
       </c>
       <c r="B7" t="n">
-        <v>8436</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,47 +1265,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544335</v>
+        <v>544309</v>
       </c>
       <c r="R7" t="n">
-        <v>6599931</v>
+        <v>6599888</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,40 +1335,49 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121780985</v>
+        <v>121780398</v>
       </c>
       <c r="B8" t="n">
-        <v>97067</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,27 +1390,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1405,10 +1423,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544320</v>
+        <v>544439</v>
       </c>
       <c r="R8" t="n">
-        <v>6599846</v>
+        <v>6599807</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121774673</v>
+        <v>121780985</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>97067</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,50 +1498,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544346</v>
+        <v>544320</v>
       </c>
       <c r="R9" t="n">
-        <v>6599874</v>
+        <v>6599846</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,19 +1563,9 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,12 +1581,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121780824</v>
+        <v>121776204</v>
       </c>
       <c r="B4" t="n">
-        <v>8436</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,47 +907,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544335</v>
+        <v>544311</v>
       </c>
       <c r="R4" t="n">
-        <v>6599931</v>
+        <v>6599894</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,40 +977,49 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121776204</v>
+        <v>121780824</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>8436</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,47 +1028,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544311</v>
+        <v>544335</v>
       </c>
       <c r="R5" t="n">
-        <v>6599894</v>
+        <v>6599931</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,39 +1098,30 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121781128</v>
+        <v>121780398</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544423</v>
+        <v>544439</v>
       </c>
       <c r="R2" t="n">
-        <v>6599802</v>
+        <v>6599807</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -895,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121776204</v>
+        <v>121776215</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -930,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -944,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544311</v>
+        <v>544309</v>
       </c>
       <c r="R4" t="n">
-        <v>6599894</v>
+        <v>6599888</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121780824</v>
+        <v>121780985</v>
       </c>
       <c r="B5" t="n">
-        <v>8436</v>
+        <v>97067</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,32 +1034,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544335</v>
+        <v>544320</v>
       </c>
       <c r="R5" t="n">
-        <v>6599931</v>
+        <v>6599846</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1253,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121776215</v>
+        <v>121781128</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,47 +1262,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544309</v>
+        <v>544423</v>
       </c>
       <c r="R7" t="n">
-        <v>6599888</v>
+        <v>6599802</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,19 +1331,9 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,22 +1348,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121780398</v>
+        <v>121780824</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>8436</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,21 +1376,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1423,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544439</v>
+        <v>544335</v>
       </c>
       <c r="R8" t="n">
-        <v>6599807</v>
+        <v>6599931</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1486,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121780985</v>
+        <v>121776204</v>
       </c>
       <c r="B9" t="n">
-        <v>97067</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,42 +1484,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544320</v>
+        <v>544311</v>
       </c>
       <c r="R9" t="n">
-        <v>6599846</v>
+        <v>6599894</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,30 +1554,39 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121780398</v>
+        <v>121776204</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>98131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544439</v>
+        <v>544311</v>
       </c>
       <c r="R2" t="n">
-        <v>6599807</v>
+        <v>6599894</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,40 +757,49 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121780897</v>
+        <v>121780398</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,33 +808,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -835,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544338</v>
+        <v>544439</v>
       </c>
       <c r="R3" t="n">
-        <v>6599919</v>
+        <v>6599807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,6 +889,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121776215</v>
+        <v>121780985</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>97085</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,47 +920,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544309</v>
+        <v>544320</v>
       </c>
       <c r="R4" t="n">
-        <v>6599888</v>
+        <v>6599846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,49 +985,40 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121780985</v>
+        <v>121776215</v>
       </c>
       <c r="B5" t="n">
-        <v>97067</v>
+        <v>98131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,42 +1027,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544320</v>
+        <v>544309</v>
       </c>
       <c r="R5" t="n">
-        <v>6599846</v>
+        <v>6599888</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,40 +1097,49 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121774673</v>
+        <v>121780897</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>57381</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,50 +1148,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544346</v>
+        <v>544338</v>
       </c>
       <c r="R6" t="n">
-        <v>6599874</v>
+        <v>6599919</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,50 +1217,39 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121781128</v>
+        <v>121780824</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>8436</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,33 +1258,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1298,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544423</v>
+        <v>544335</v>
       </c>
       <c r="R7" t="n">
-        <v>6599802</v>
+        <v>6599931</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,6 +1339,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1360,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121780824</v>
+        <v>121781128</v>
       </c>
       <c r="B8" t="n">
-        <v>8436</v>
+        <v>57381</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,34 +1370,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1409,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544335</v>
+        <v>544423</v>
       </c>
       <c r="R8" t="n">
-        <v>6599931</v>
+        <v>6599802</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,7 +1450,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1472,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121776204</v>
+        <v>121774673</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,7 +1503,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1515,16 +1511,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544311</v>
+        <v>544346</v>
       </c>
       <c r="R9" t="n">
-        <v>6599894</v>
+        <v>6599874</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,6 +1574,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>121780679</v>
       </c>
       <c r="B10" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121780985</v>
+        <v>121776215</v>
       </c>
       <c r="B4" t="n">
-        <v>97085</v>
+        <v>98131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,42 +920,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544320</v>
+        <v>544309</v>
       </c>
       <c r="R4" t="n">
-        <v>6599846</v>
+        <v>6599888</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,40 +990,49 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121776215</v>
+        <v>121780985</v>
       </c>
       <c r="B5" t="n">
-        <v>98131</v>
+        <v>97085</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,47 +1041,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544309</v>
+        <v>544320</v>
       </c>
       <c r="R5" t="n">
-        <v>6599888</v>
+        <v>6599846</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,39 +1106,30 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -1493,7 +1493,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121780897</v>
+        <v>121781128</v>
       </c>
       <c r="B9" t="n">
         <v>57390</v>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544338</v>
+        <v>544423</v>
       </c>
       <c r="R9" t="n">
-        <v>6599919</v>
+        <v>6599802</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121781128</v>
+        <v>121780897</v>
       </c>
       <c r="B10" t="n">
         <v>57390</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544423</v>
+        <v>544338</v>
       </c>
       <c r="R10" t="n">
-        <v>6599802</v>
+        <v>6599919</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -1493,7 +1493,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121781128</v>
+        <v>121780897</v>
       </c>
       <c r="B9" t="n">
         <v>57390</v>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544423</v>
+        <v>544338</v>
       </c>
       <c r="R9" t="n">
-        <v>6599802</v>
+        <v>6599919</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121780897</v>
+        <v>121781128</v>
       </c>
       <c r="B10" t="n">
         <v>57390</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544338</v>
+        <v>544423</v>
       </c>
       <c r="R10" t="n">
-        <v>6599919</v>
+        <v>6599802</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -1493,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121780897</v>
+        <v>121781128</v>
       </c>
       <c r="B9" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544338</v>
+        <v>544423</v>
       </c>
       <c r="R9" t="n">
-        <v>6599919</v>
+        <v>6599802</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121781128</v>
+        <v>121780897</v>
       </c>
       <c r="B10" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544423</v>
+        <v>544338</v>
       </c>
       <c r="R10" t="n">
-        <v>6599802</v>
+        <v>6599919</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -1511,11 +1511,6 @@
       <c r="E9" t="n">
         <v>100049</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1620,11 +1615,6 @@
       </c>
       <c r="E10" t="n">
         <v>100049</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -1496,7 +1496,7 @@
         <v>121781128</v>
       </c>
       <c r="B9" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,6 +1510,11 @@
       </c>
       <c r="E9" t="n">
         <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1601,7 +1606,7 @@
         <v>121780897</v>
       </c>
       <c r="B10" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,6 +1620,11 @@
       </c>
       <c r="E10" t="n">
         <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>121776204</v>
       </c>
       <c r="B2" t="n">
-        <v>98159</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,59 +791,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121780398</v>
+        <v>121776215</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544439</v>
+        <v>544309</v>
       </c>
       <c r="R3" t="n">
-        <v>6599807</v>
+        <v>6599888</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,45 +868,49 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121780824</v>
+        <v>121780985</v>
       </c>
       <c r="B4" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,32 +918,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544335</v>
+        <v>544320</v>
       </c>
       <c r="R4" t="n">
-        <v>6599931</v>
+        <v>6599846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,62 +1009,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121774673</v>
+        <v>121780897</v>
       </c>
       <c r="B5" t="n">
-        <v>98159</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544346</v>
+        <v>544338</v>
       </c>
       <c r="R5" t="n">
-        <v>6599874</v>
+        <v>6599919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,99 +1085,82 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121776215</v>
+        <v>121781128</v>
       </c>
       <c r="B6" t="n">
-        <v>98159</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hagalund, Hagalund, Vstm</t>
+          <t>Sundänge, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544309</v>
+        <v>544423</v>
       </c>
       <c r="R6" t="n">
-        <v>6599888</v>
+        <v>6599802</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,19 +1190,9 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,27 +1207,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121780985</v>
+        <v>121780398</v>
       </c>
       <c r="B7" t="n">
-        <v>97113</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,27 +1230,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1310,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544320</v>
+        <v>544439</v>
       </c>
       <c r="R7" t="n">
-        <v>6599846</v>
+        <v>6599807</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,51 +1326,43 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121780679</v>
+        <v>121780824</v>
       </c>
       <c r="B8" t="n">
-        <v>98159</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1425,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544416</v>
+        <v>544335</v>
       </c>
       <c r="R8" t="n">
-        <v>6599823</v>
+        <v>6599931</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,11 +1406,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 250 st. bladrosetter. Möjligtvis fler. Vid olika platser, intill varandra. Vid gran och tall, vid en liten låga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,58 +1433,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121781128</v>
+        <v>121774673</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>Hagalund, Hagalund, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544423</v>
+        <v>544346</v>
       </c>
       <c r="R9" t="n">
-        <v>6599802</v>
+        <v>6599874</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,76 +1513,86 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121780897</v>
+        <v>121780679</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1651,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544338</v>
+        <v>544416</v>
       </c>
       <c r="R10" t="n">
-        <v>6599919</v>
+        <v>6599823</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,12 +1638,18 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca 250 st. bladrosetter. Möjligtvis fler. Vid olika platser, intill varandra. Vid gran och tall, vid en liten låga.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56048-2024 artfynd.xlsx
+++ b/artfynd/A 56048-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121780897</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121781128</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121780398</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121780824</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121774673</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121776204</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,6 +1483,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121776215</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121780679</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1665,8 +1710,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121780985</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>